--- a/data/trans_bre/P1429-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1429-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,51</t>
+          <t>2,33</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>308,26%</t>
+          <t>317,61%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,52</t>
+          <t>1,11; 5,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 7,23</t>
+          <t>2,22; 7,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 7,14</t>
+          <t>2,14; 7,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,48</t>
+          <t>0,67; 3,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,84; 1719,75</t>
+          <t>20,01; 1626,82</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,13</t>
+          <t>3,06</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1873,11%</t>
+          <t>1718,87%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,44</t>
+          <t>4,55; 9,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,22</t>
+          <t>0,14; 3,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,3</t>
+          <t>1,81; 5,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,64</t>
+          <t>1,94; 4,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,02; —</t>
+          <t>-55,8; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,41</t>
+          <t>4,4</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1492,64%</t>
+          <t>1540,81%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,35</t>
+          <t>1,84; 6,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,37</t>
+          <t>0,94; 5,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,26</t>
+          <t>0,37; 4,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,86; 6,28</t>
+          <t>2,89; 6,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,26</t>
+          <t>5,95</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>172,2%</t>
+          <t>283,8%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 6,33</t>
+          <t>2,48; 6,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 11,19</t>
+          <t>5,24; 11,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 9,12</t>
+          <t>3,34; 9,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 7,62</t>
+          <t>2,72; 8,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>190,13; —</t>
+          <t>206,45; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,62; 702,33</t>
+          <t>31,71; 926,91</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,16</t>
+          <t>3,96</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>495,45%</t>
+          <t>508,57%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 3,84</t>
+          <t>-0,26; 4,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,81</t>
+          <t>1,8; 7,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,5</t>
+          <t>0,0; 3,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,4; 6,67</t>
+          <t>1,92; 5,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>87,41; 2340,57</t>
+          <t>79,32; 2102,45</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,54</t>
+          <t>4,56</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>275,83%</t>
+          <t>287,23%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,24; 7,05</t>
+          <t>2,33; 7,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,87</t>
+          <t>0,79; 4,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 3,47</t>
+          <t>-1,08; 3,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,23; 6,89</t>
+          <t>2,12; 6,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>75,78; 958,32</t>
+          <t>62,58; 870,75</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,33</t>
+          <t>4,93</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>457,8%</t>
+          <t>690,67%</t>
         </is>
       </c>
     </row>
@@ -1260,27 +1260,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,74</t>
+          <t>1,53; 4,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,86; 6,2</t>
+          <t>2,87; 6,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,9</t>
+          <t>2,19; 5,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,35</t>
+          <t>3,67; 6,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>103,69; 2317,64</t>
+          <t>88,37; 2232,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1290,12 +1290,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>141,39; 2048,71</t>
+          <t>110,27; 1799,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>70,64; 1566,64</t>
+          <t>231,38; 2862,81</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,89</t>
+          <t>2,65</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>459,73%</t>
+          <t>325,66%</t>
         </is>
       </c>
     </row>
@@ -1360,27 +1360,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,31</t>
+          <t>-0,93; 3,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,16</t>
+          <t>2,26; 4,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,91</t>
+          <t>1,55; 3,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,1</t>
+          <t>1,46; 3,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,85; 116,34</t>
+          <t>-20,88; 126,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>155,33; 1587,75</t>
+          <t>106,66; 918,95</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,58</t>
+          <t>3,92</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>436,41%</t>
+          <t>467,76%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,06</t>
+          <t>2,51; 4,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,6</t>
+          <t>3,16; 4,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,47; 3,85</t>
+          <t>2,44; 3,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,73; 4,31</t>
+          <t>3,29; 4,57</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>191,88; 533,47</t>
+          <t>190,19; 498,8</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>707,08; 6020,21</t>
+          <t>780,69; 5624,63</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>442,93; 1859,53</t>
+          <t>477,85; 1886,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>230,18; 733,67</t>
+          <t>261,49; 724,91</t>
         </is>
       </c>
     </row>
